--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_6/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_6/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9317,0.0130,0.0961,0.0028</t>
-  </si>
-  <si>
-    <t>0.9347,0.0072,0.0971,0.0046</t>
-  </si>
-  <si>
-    <t>0.9430,0.0117,0.0680,0.0024</t>
-  </si>
-  <si>
-    <t>0.9475,0.0149,0.0425,0.0053</t>
-  </si>
-  <si>
-    <t>0.9383,0.0232,0.0580,0.0029</t>
-  </si>
-  <si>
-    <t>0.9718,0.0114,0.0205,0.0015</t>
-  </si>
-  <si>
-    <t>0.9065,0.0311,0.0833,0.0034</t>
-  </si>
-  <si>
-    <t>0.9545,0.0214,0.0320,0.0030</t>
-  </si>
-  <si>
-    <t>0.9501,0.0206,0.0344,0.0029</t>
-  </si>
-  <si>
-    <t>0.9309,0.0265,0.0546,0.0058</t>
-  </si>
-  <si>
-    <t>0.9464,0.0222,0.0370,0.0035</t>
-  </si>
-  <si>
-    <t>0.9505,0.0233,0.0371,0.0034</t>
-  </si>
-  <si>
-    <t>0.8496,0.0150,0.2245,0.0038</t>
-  </si>
-  <si>
-    <t>0.3845,0.0126,0.7563,0.0027</t>
-  </si>
-  <si>
-    <t>0.8816,0.0059,0.2412,0.0017</t>
-  </si>
-  <si>
-    <t>0.5395,0.0114,0.6292,0.0021</t>
-  </si>
-  <si>
-    <t>0.9526,0.0089,0.0643,0.0023</t>
-  </si>
-  <si>
-    <t>0.3335,0.1851,0.4153,0.0053</t>
-  </si>
-  <si>
-    <t>0.6476,0.0696,0.3542,0.0048</t>
-  </si>
-  <si>
-    <t>0.9108,0.0296,0.0713,0.0044</t>
-  </si>
-  <si>
-    <t>0.8309,0.0844,0.0821,0.0037</t>
-  </si>
-  <si>
-    <t>0.5013,0.1677,0.2612,0.0036</t>
-  </si>
-  <si>
-    <t>0.7649,0.0069,0.4471,0.0025</t>
-  </si>
-  <si>
-    <t>0.7320,0.0102,0.4636,0.0027</t>
-  </si>
-  <si>
-    <t>0.6012,0.0035,0.6888,0.0011</t>
-  </si>
-  <si>
-    <t>0.5854,0.0054,0.6549,0.0019</t>
-  </si>
-  <si>
-    <t>0.6373,0.0069,0.5921,0.0022</t>
-  </si>
-  <si>
-    <t>0.6264,0.0032,0.6666,0.0013</t>
-  </si>
-  <si>
-    <t>0.3182,0.0082,0.8374,0.0018</t>
-  </si>
-  <si>
-    <t>0.8925,0.0173,0.1392,0.0024</t>
-  </si>
-  <si>
-    <t>0.7955,0.0185,0.2741,0.0030</t>
-  </si>
-  <si>
-    <t>0.0652,0.0154,0.9534,0.0079</t>
-  </si>
-  <si>
-    <t>0.6649,0.0264,0.4187,0.0027</t>
-  </si>
-  <si>
-    <t>0.9179,0.0153,0.1076,0.0032</t>
-  </si>
-  <si>
-    <t>0.8882,0.0269,0.1123,0.0042</t>
-  </si>
-  <si>
-    <t>0.8731,0.0296,0.1411,0.0045</t>
-  </si>
-  <si>
-    <t>0.8762,0.0384,0.1309,0.0052</t>
-  </si>
-  <si>
-    <t>0.2455,0.0164,0.8310,0.0036</t>
-  </si>
-  <si>
-    <t>0.3839,0.0047,0.8179,0.0020</t>
-  </si>
-  <si>
-    <t>0.3624,0.0043,0.8334,0.0011</t>
-  </si>
-  <si>
-    <t>0.5323,0.0143,0.6478,0.0033</t>
-  </si>
-  <si>
-    <t>0.2497,0.0060,0.8894,0.0010</t>
-  </si>
-  <si>
-    <t>0.3083,0.0870,0.6495,0.0052</t>
-  </si>
-  <si>
-    <t>0.2856,0.0090,0.8341,0.0021</t>
-  </si>
-  <si>
-    <t>0.9455,0.0113,0.0646,0.0017</t>
-  </si>
-  <si>
-    <t>0.1337,0.3765,0.5401,0.0045</t>
-  </si>
-  <si>
-    <t>0.0837,0.1989,0.7951,0.0028</t>
-  </si>
-  <si>
-    <t>0.3912,0.0353,0.6897,0.0028</t>
-  </si>
-  <si>
-    <t>0.0973,0.0171,0.9392,0.0036</t>
-  </si>
-  <si>
-    <t>0.1393,0.0064,0.9340,0.0016</t>
-  </si>
-  <si>
-    <t>0.5029,0.0060,0.7200,0.0023</t>
-  </si>
-  <si>
-    <t>0.5503,0.0054,0.6844,0.0021</t>
-  </si>
-  <si>
-    <t>0.1267,0.0089,0.9355,0.0032</t>
-  </si>
-  <si>
-    <t>0.4825,0.0103,0.6948,0.0025</t>
-  </si>
-  <si>
-    <t>0.9414,0.0215,0.0504,0.0025</t>
-  </si>
-  <si>
-    <t>0.9520,0.0188,0.0389,0.0028</t>
-  </si>
-  <si>
-    <t>0.9549,0.0196,0.0300,0.0032</t>
-  </si>
-  <si>
-    <t>0.3626,0.0222,0.7397,0.0048</t>
-  </si>
-  <si>
-    <t>0.9690,0.0137,0.0216,0.0017</t>
-  </si>
-  <si>
-    <t>0.9447,0.0197,0.0466,0.0027</t>
-  </si>
-  <si>
-    <t>0.9553,0.0210,0.0297,0.0029</t>
-  </si>
-  <si>
-    <t>0.0737,0.0281,0.9378,0.0018</t>
-  </si>
-  <si>
-    <t>0.0954,0.0072,0.9494,0.0013</t>
-  </si>
-  <si>
-    <t>0.2550,0.0081,0.8621,0.0023</t>
-  </si>
-  <si>
-    <t>0.0318,0.0422,0.9695,0.0014</t>
-  </si>
-  <si>
-    <t>0.1231,0.0049,0.9431,0.0013</t>
-  </si>
-  <si>
-    <t>0.7377,0.0337,0.2893,0.0023</t>
-  </si>
-  <si>
-    <t>0.1240,0.3854,0.5387,0.0057</t>
-  </si>
-  <si>
-    <t>0.8711,0.0273,0.1532,0.0037</t>
-  </si>
-  <si>
-    <t>0.8088,0.0180,0.2919,0.0032</t>
-  </si>
-  <si>
-    <t>0.7502,0.0163,0.3598,0.0033</t>
-  </si>
-  <si>
-    <t>0.1102,0.0444,0.9018,0.0019</t>
-  </si>
-  <si>
-    <t>0.0705,0.0676,0.9192,0.0015</t>
-  </si>
-  <si>
-    <t>0.0173,0.0324,0.9818,0.0014</t>
-  </si>
-  <si>
-    <t>0.0376,0.0415,0.9679,0.0014</t>
-  </si>
-  <si>
-    <t>0.9074,0.0095,0.1590,0.0035</t>
-  </si>
-  <si>
-    <t>0.9646,0.0077,0.0278,0.0042</t>
-  </si>
-  <si>
-    <t>0.9604,0.0092,0.0370,0.0032</t>
-  </si>
-  <si>
-    <t>0.9550,0.0088,0.0574,0.0032</t>
-  </si>
-  <si>
-    <t>0.9592,0.0073,0.0535,0.0036</t>
-  </si>
-  <si>
-    <t>0.9492,0.0073,0.0770,0.0028</t>
-  </si>
-  <si>
-    <t>0.0539,0.0567,0.9297,0.0018</t>
-  </si>
-  <si>
-    <t>0.0346,0.0160,0.9782,0.0010</t>
-  </si>
-  <si>
-    <t>0.1043,0.0183,0.9229,0.0010</t>
-  </si>
-  <si>
-    <t>0.1437,0.0138,0.9066,0.0016</t>
-  </si>
-  <si>
-    <t>0.0539,0.0278,0.9581,0.0010</t>
-  </si>
-  <si>
-    <t>0.3772,0.0140,0.7651,0.0018</t>
-  </si>
-  <si>
-    <t>0.9613,0.0151,0.0338,0.0015</t>
-  </si>
-  <si>
-    <t>0.9551,0.0196,0.0291,0.0026</t>
-  </si>
-  <si>
-    <t>0.9408,0.0275,0.0387,0.0042</t>
-  </si>
-  <si>
-    <t>0.9355,0.0329,0.0394,0.0032</t>
-  </si>
-  <si>
-    <t>0.9343,0.0336,0.0385,0.0026</t>
-  </si>
-  <si>
-    <t>0.9556,0.0202,0.0357,0.0030</t>
-  </si>
-  <si>
-    <t>0.9622,0.0132,0.0311,0.0026</t>
-  </si>
-  <si>
-    <t>0.9553,0.0146,0.0439,0.0034</t>
-  </si>
-  <si>
-    <t>0.9717,0.0130,0.0179,0.0021</t>
-  </si>
-  <si>
-    <t>0.9238,0.0353,0.0542,0.0049</t>
-  </si>
-  <si>
-    <t>0.9688,0.0119,0.0189,0.0034</t>
-  </si>
-  <si>
-    <t>0.9304,0.0260,0.0596,0.0043</t>
-  </si>
-  <si>
-    <t>0.9631,0.0133,0.0278,0.0034</t>
-  </si>
-  <si>
-    <t>0.9534,0.0207,0.0304,0.0026</t>
-  </si>
-  <si>
-    <t>0.9621,0.0139,0.0321,0.0022</t>
-  </si>
-  <si>
-    <t>0.9484,0.0199,0.0445,0.0030</t>
-  </si>
-  <si>
-    <t>0.2338,0.0068,0.8806,0.0028</t>
-  </si>
-  <si>
-    <t>0.1256,0.0077,0.9247,0.0025</t>
-  </si>
-  <si>
-    <t>0.8604,0.0103,0.2450,0.0026</t>
-  </si>
-  <si>
-    <t>0.8220,0.0056,0.3742,0.0013</t>
-  </si>
-  <si>
-    <t>0.6067,0.1224,0.2652,0.0045</t>
-  </si>
-  <si>
-    <t>0.7528,0.0583,0.2154,0.0034</t>
-  </si>
-  <si>
-    <t>0.8967,0.0358,0.0872,0.0038</t>
-  </si>
-  <si>
-    <t>0.8932,0.0311,0.0959,0.0035</t>
-  </si>
-  <si>
-    <t>0.8010,0.0682,0.1369,0.0055</t>
-  </si>
-  <si>
-    <t>0.5256,0.1535,0.2477,0.0052</t>
-  </si>
-  <si>
-    <t>0.8830,0.0437,0.0937,0.0039</t>
-  </si>
-  <si>
-    <t>0.8321,0.0165,0.2520,0.0026</t>
-  </si>
-  <si>
-    <t>0.7734,0.0049,0.4510,0.0016</t>
-  </si>
-  <si>
-    <t>0.8757,0.0143,0.1980,0.0023</t>
-  </si>
-  <si>
-    <t>0.8463,0.0090,0.2696,0.0023</t>
-  </si>
-  <si>
-    <t>0.9077,0.0107,0.1415,0.0041</t>
-  </si>
-  <si>
-    <t>0.4324,0.0959,0.5204,0.0030</t>
-  </si>
-  <si>
-    <t>0.3278,0.0701,0.6105,0.0036</t>
-  </si>
-  <si>
-    <t>0.8874,0.0092,0.2030,0.0026</t>
-  </si>
-  <si>
-    <t>0.0246,0.3346,0.9170,0.0042</t>
-  </si>
-  <si>
-    <t>0.7646,0.0530,0.2182,0.0035</t>
-  </si>
-  <si>
-    <t>0.8825,0.0393,0.0972,0.0034</t>
-  </si>
-  <si>
-    <t>0.9378,0.0176,0.0695,0.0034</t>
-  </si>
-  <si>
-    <t>0.9634,0.0113,0.0351,0.0015</t>
-  </si>
-  <si>
-    <t>0.9723,0.0097,0.0210,0.0018</t>
-  </si>
-  <si>
-    <t>0.9311,0.0159,0.0820,0.0027</t>
-  </si>
-  <si>
-    <t>0.9557,0.0130,0.0433,0.0032</t>
-  </si>
-  <si>
-    <t>0.9481,0.0191,0.0390,0.0043</t>
-  </si>
-  <si>
-    <t>0.9269,0.0190,0.0879,0.0019</t>
-  </si>
-  <si>
-    <t>0.9597,0.0126,0.0408,0.0018</t>
-  </si>
-  <si>
-    <t>0.9428,0.0149,0.0648,0.0020</t>
-  </si>
-  <si>
-    <t>0.0715,0.0201,0.9373,0.0016</t>
-  </si>
-  <si>
-    <t>0.3873,0.0204,0.7317,0.0026</t>
-  </si>
-  <si>
-    <t>0.2968,0.0074,0.8470,0.0026</t>
-  </si>
-  <si>
-    <t>0.5301,0.0091,0.6712,0.0019</t>
-  </si>
-  <si>
-    <t>0.9168,0.0058,0.1616,0.0016</t>
-  </si>
-  <si>
-    <t>0.9489,0.0098,0.0680,0.0023</t>
-  </si>
-  <si>
-    <t>0.8963,0.0054,0.2170,0.0013</t>
-  </si>
-  <si>
-    <t>0.9011,0.0119,0.1564,0.0036</t>
-  </si>
-  <si>
-    <t>0.9234,0.0082,0.1290,0.0030</t>
-  </si>
-  <si>
-    <t>0.8882,0.0157,0.0992,0.0252</t>
-  </si>
-  <si>
-    <t>0.9407,0.0117,0.0718,0.0051</t>
-  </si>
-  <si>
-    <t>0.9625,0.0055,0.0514,0.0035</t>
-  </si>
-  <si>
-    <t>0.0392,0.2869,0.8925,0.0041</t>
-  </si>
-  <si>
-    <t>0.9454,0.0159,0.0564,0.0025</t>
-  </si>
-  <si>
-    <t>0.9112,0.0348,0.0681,0.0042</t>
-  </si>
-  <si>
-    <t>0.9548,0.0150,0.0438,0.0023</t>
-  </si>
-  <si>
-    <t>0.8929,0.0376,0.0877,0.0040</t>
-  </si>
-  <si>
-    <t>0.9683,0.0084,0.0325,0.0023</t>
-  </si>
-  <si>
-    <t>0.9334,0.0168,0.0821,0.0043</t>
-  </si>
-  <si>
-    <t>0.9632,0.0134,0.0330,0.0025</t>
-  </si>
-  <si>
-    <t>0.0697,0.0152,0.9500,0.0073</t>
-  </si>
-  <si>
-    <t>0.9755,0.0058,0.0324,0.0014</t>
-  </si>
-  <si>
-    <t>0.9628,0.0097,0.0443,0.0025</t>
-  </si>
-  <si>
-    <t>0.8866,0.0260,0.1325,0.0037</t>
-  </si>
-  <si>
-    <t>0.9363,0.0163,0.0633,0.0029</t>
-  </si>
-  <si>
-    <t>0.8867,0.0190,0.1392,0.0026</t>
-  </si>
-  <si>
-    <t>0.5405,0.0254,0.5843,0.0045</t>
-  </si>
-  <si>
-    <t>0.9191,0.0177,0.1065,0.0028</t>
-  </si>
-  <si>
-    <t>0.9433,0.0122,0.0677,0.0018</t>
-  </si>
-  <si>
-    <t>0.9600,0.0128,0.0323,0.0026</t>
-  </si>
-  <si>
-    <t>0.9624,0.0159,0.0302,0.0025</t>
-  </si>
-  <si>
-    <t>0.9435,0.0232,0.0434,0.0028</t>
-  </si>
-  <si>
-    <t>0.9763,0.0080,0.0232,0.0021</t>
-  </si>
-  <si>
-    <t>0.9376,0.0229,0.0469,0.0036</t>
-  </si>
-  <si>
-    <t>0.9297,0.0283,0.0522,0.0026</t>
-  </si>
-  <si>
-    <t>0.9570,0.0183,0.0278,0.0027</t>
-  </si>
-  <si>
-    <t>0.9588,0.0216,0.0198,0.0030</t>
-  </si>
-  <si>
-    <t>0.5503,0.1556,0.2646,0.0056</t>
-  </si>
-  <si>
-    <t>0.8834,0.0491,0.0864,0.0031</t>
-  </si>
-  <si>
-    <t>0.9352,0.0200,0.0626,0.0022</t>
-  </si>
-  <si>
-    <t>0.9085,0.0208,0.1119,0.0029</t>
-  </si>
-  <si>
-    <t>0.9554,0.0190,0.0298,0.0017</t>
-  </si>
-  <si>
-    <t>0.9558,0.0166,0.0322,0.0022</t>
-  </si>
-  <si>
-    <t>0.9499,0.0218,0.0362,0.0040</t>
-  </si>
-  <si>
-    <t>0.9392,0.0190,0.0616,0.0045</t>
-  </si>
-  <si>
-    <t>0.1180,0.0065,0.9431,0.0026</t>
-  </si>
-  <si>
-    <t>0.9418,0.0196,0.0509,0.0031</t>
-  </si>
-  <si>
-    <t>0.1391,0.0036,0.9439,0.0011</t>
-  </si>
-  <si>
-    <t>0.5039,0.0066,0.7215,0.0023</t>
-  </si>
-  <si>
-    <t>0.2990,0.0065,0.8472,0.0011</t>
-  </si>
-  <si>
-    <t>0.1912,0.0137,0.8681,0.0021</t>
-  </si>
-  <si>
-    <t>0.4944,0.0080,0.7069,0.0017</t>
-  </si>
-  <si>
-    <t>0.4674,0.0040,0.7721,0.0012</t>
-  </si>
-  <si>
-    <t>0.2654,0.0136,0.8329,0.0017</t>
-  </si>
-  <si>
-    <t>0.8142,0.0096,0.3342,0.0023</t>
-  </si>
-  <si>
-    <t>0.8321,0.0132,0.2893,0.0033</t>
-  </si>
-  <si>
-    <t>0.6808,0.0138,0.4507,0.0031</t>
-  </si>
-  <si>
-    <t>0.8125,0.0321,0.2167,0.0033</t>
-  </si>
-  <si>
-    <t>0.6300,0.0199,0.5020,0.0027</t>
-  </si>
-  <si>
-    <t>0.8234,0.0110,0.3043,0.0018</t>
-  </si>
-  <si>
-    <t>0.6608,0.0099,0.5172,0.0024</t>
-  </si>
-  <si>
-    <t>0.8886,0.0061,0.2422,0.0012</t>
-  </si>
-  <si>
-    <t>0.9124,0.0314,0.0625,0.0023</t>
-  </si>
-  <si>
-    <t>0.8762,0.0365,0.1119,0.0037</t>
-  </si>
-  <si>
-    <t>0.9263,0.0269,0.0636,0.0023</t>
-  </si>
-  <si>
-    <t>0.9114,0.0342,0.0650,0.0037</t>
-  </si>
-  <si>
-    <t>0.9220,0.0292,0.0667,0.0035</t>
-  </si>
-  <si>
-    <t>0.8149,0.0100,0.3354,0.0020</t>
-  </si>
-  <si>
-    <t>0.8855,0.0101,0.1952,0.0023</t>
-  </si>
-  <si>
-    <t>0.8653,0.0093,0.2329,0.0023</t>
-  </si>
-  <si>
-    <t>0.8541,0.0058,0.3025,0.0015</t>
-  </si>
-  <si>
-    <t>0.9304,0.0082,0.1177,0.0023</t>
-  </si>
-  <si>
-    <t>0.2982,0.0044,0.8548,0.0017</t>
-  </si>
-  <si>
-    <t>0.4921,0.0064,0.7206,0.0019</t>
-  </si>
-  <si>
-    <t>0.2769,0.0084,0.8568,0.0013</t>
-  </si>
-  <si>
-    <t>0.3424,0.0049,0.8273,0.0016</t>
-  </si>
-  <si>
-    <t>0.5230,0.0071,0.7062,0.0025</t>
-  </si>
-  <si>
-    <t>0.9508,0.0196,0.0329,0.0047</t>
-  </si>
-  <si>
-    <t>0.9525,0.0100,0.0650,0.0020</t>
-  </si>
-  <si>
-    <t>0.9381,0.0196,0.0634,0.0039</t>
-  </si>
-  <si>
-    <t>0.8938,0.0377,0.0921,0.0039</t>
-  </si>
-  <si>
-    <t>0.9355,0.0290,0.0478,0.0026</t>
-  </si>
-  <si>
-    <t>0.9087,0.0398,0.0557,0.0036</t>
-  </si>
-  <si>
-    <t>0.9310,0.0288,0.0501,0.0034</t>
-  </si>
-  <si>
-    <t>0.9493,0.0168,0.0513,0.0033</t>
-  </si>
-  <si>
-    <t>0.8414,0.0175,0.2300,0.0038</t>
-  </si>
-  <si>
-    <t>0.8903,0.0269,0.1152,0.0040</t>
-  </si>
-  <si>
-    <t>0.9264,0.0113,0.1020,0.0018</t>
-  </si>
-  <si>
-    <t>0.2058,0.0040,0.9042,0.0013</t>
-  </si>
-  <si>
-    <t>0.1529,0.0082,0.9168,0.0025</t>
-  </si>
-  <si>
-    <t>0.2323,0.0167,0.8286,0.0031</t>
-  </si>
-  <si>
-    <t>0.1036,0.0047,0.9496,0.0023</t>
-  </si>
-  <si>
-    <t>0.5103,0.0098,0.6611,0.0022</t>
-  </si>
-  <si>
-    <t>0.0683,0.0135,0.9544,0.0026</t>
-  </si>
-  <si>
-    <t>0.4198,0.0131,0.7353,0.0034</t>
-  </si>
-  <si>
-    <t>0.3666,0.0166,0.7324,0.0050</t>
-  </si>
-  <si>
-    <t>0.9379,0.0060,0.1111,0.0012</t>
-  </si>
-  <si>
-    <t>0.9257,0.0050,0.1532,0.0015</t>
-  </si>
-  <si>
-    <t>0.9309,0.0073,0.1260,0.0013</t>
-  </si>
-  <si>
-    <t>0.9716,0.0144,0.0189,0.0019</t>
-  </si>
-  <si>
-    <t>0.9295,0.0298,0.0454,0.0053</t>
-  </si>
-  <si>
-    <t>0.9559,0.0159,0.0393,0.0029</t>
-  </si>
-  <si>
-    <t>0.9007,0.0421,0.0786,0.0039</t>
-  </si>
-  <si>
-    <t>0.9306,0.0261,0.0616,0.0040</t>
-  </si>
-  <si>
-    <t>0.9345,0.0282,0.0449,0.0032</t>
-  </si>
-  <si>
-    <t>0.9237,0.0336,0.0486,0.0056</t>
-  </si>
-  <si>
-    <t>0.9573,0.0179,0.0324,0.0030</t>
-  </si>
-  <si>
-    <t>0.3448,0.0116,0.7913,0.0020</t>
-  </si>
-  <si>
-    <t>0.0418,0.0119,0.9690,0.0018</t>
-  </si>
-  <si>
-    <t>0.0792,0.0094,0.9578,0.0018</t>
-  </si>
-  <si>
-    <t>0.8111,0.0051,0.3996,0.0012</t>
-  </si>
-  <si>
-    <t>0.4914,0.0046,0.7443,0.0017</t>
-  </si>
-  <si>
-    <t>0.7290,0.0165,0.4098,0.0028</t>
-  </si>
-  <si>
-    <t>0.7009,0.0069,0.5076,0.0026</t>
-  </si>
-  <si>
-    <t>0.4275,0.0119,0.7437,0.0035</t>
-  </si>
-  <si>
-    <t>0.9276,0.0075,0.1243,0.0021</t>
-  </si>
-  <si>
-    <t>0.8940,0.0073,0.2055,0.0038</t>
-  </si>
-  <si>
-    <t>0.9405,0.0089,0.0879,0.0044</t>
-  </si>
-  <si>
-    <t>0.9514,0.0063,0.0595,0.0051</t>
-  </si>
-  <si>
-    <t>0.9585,0.0064,0.0433,0.0064</t>
-  </si>
-  <si>
-    <t>0.8817,0.0144,0.1836,0.0032</t>
+    <t>0.9653,0.0087,0.0408,0.0024</t>
+  </si>
+  <si>
+    <t>0.9444,0.0079,0.0691,0.0057</t>
+  </si>
+  <si>
+    <t>0.9233,0.0159,0.0977,0.0028</t>
+  </si>
+  <si>
+    <t>0.9589,0.0068,0.0521,0.0027</t>
+  </si>
+  <si>
+    <t>0.9416,0.0227,0.0510,0.0046</t>
+  </si>
+  <si>
+    <t>0.9177,0.0260,0.0777,0.0035</t>
+  </si>
+  <si>
+    <t>0.9596,0.0175,0.0304,0.0034</t>
+  </si>
+  <si>
+    <t>0.9551,0.0106,0.0574,0.0025</t>
+  </si>
+  <si>
+    <t>0.9294,0.0322,0.0477,0.0052</t>
+  </si>
+  <si>
+    <t>0.9449,0.0168,0.0515,0.0017</t>
+  </si>
+  <si>
+    <t>0.9331,0.0265,0.0480,0.0036</t>
+  </si>
+  <si>
+    <t>0.9756,0.0099,0.0165,0.0020</t>
+  </si>
+  <si>
+    <t>0.9060,0.0099,0.1458,0.0017</t>
+  </si>
+  <si>
+    <t>0.8078,0.0105,0.3366,0.0028</t>
+  </si>
+  <si>
+    <t>0.8603,0.0052,0.3165,0.0010</t>
+  </si>
+  <si>
+    <t>0.7428,0.0129,0.4142,0.0025</t>
+  </si>
+  <si>
+    <t>0.8653,0.0099,0.2559,0.0018</t>
+  </si>
+  <si>
+    <t>0.5184,0.2424,0.2128,0.0076</t>
+  </si>
+  <si>
+    <t>0.6448,0.1008,0.2352,0.0043</t>
+  </si>
+  <si>
+    <t>0.8139,0.0497,0.1682,0.0046</t>
+  </si>
+  <si>
+    <t>0.8173,0.0432,0.1597,0.0026</t>
+  </si>
+  <si>
+    <t>0.4846,0.1945,0.2763,0.0044</t>
+  </si>
+  <si>
+    <t>0.7217,0.0040,0.5216,0.0015</t>
+  </si>
+  <si>
+    <t>0.7930,0.0038,0.4490,0.0011</t>
+  </si>
+  <si>
+    <t>0.3830,0.0049,0.8222,0.0016</t>
+  </si>
+  <si>
+    <t>0.7791,0.0044,0.4514,0.0013</t>
+  </si>
+  <si>
+    <t>0.5407,0.0038,0.7157,0.0015</t>
+  </si>
+  <si>
+    <t>0.8373,0.0049,0.3541,0.0020</t>
+  </si>
+  <si>
+    <t>0.6201,0.0087,0.5825,0.0029</t>
+  </si>
+  <si>
+    <t>0.9097,0.0263,0.0856,0.0023</t>
+  </si>
+  <si>
+    <t>0.8614,0.0210,0.1784,0.0038</t>
+  </si>
+  <si>
+    <t>0.1400,0.0113,0.9265,0.0040</t>
+  </si>
+  <si>
+    <t>0.7783,0.0091,0.4169,0.0014</t>
+  </si>
+  <si>
+    <t>0.9618,0.0087,0.0487,0.0020</t>
+  </si>
+  <si>
+    <t>0.8531,0.0122,0.2400,0.0038</t>
+  </si>
+  <si>
+    <t>0.9266,0.0327,0.0541,0.0034</t>
+  </si>
+  <si>
+    <t>0.7275,0.0732,0.2397,0.0055</t>
+  </si>
+  <si>
+    <t>0.2338,0.0424,0.8062,0.0075</t>
+  </si>
+  <si>
+    <t>0.4685,0.0095,0.7459,0.0044</t>
+  </si>
+  <si>
+    <t>0.4824,0.0060,0.7448,0.0019</t>
+  </si>
+  <si>
+    <t>0.3710,0.0053,0.8407,0.0018</t>
+  </si>
+  <si>
+    <t>0.3902,0.0075,0.7988,0.0014</t>
+  </si>
+  <si>
+    <t>0.2063,0.1324,0.6405,0.0061</t>
+  </si>
+  <si>
+    <t>0.2516,0.0067,0.8738,0.0015</t>
+  </si>
+  <si>
+    <t>0.9453,0.0105,0.0711,0.0028</t>
+  </si>
+  <si>
+    <t>0.5571,0.0297,0.5141,0.0030</t>
+  </si>
+  <si>
+    <t>0.2844,0.1020,0.6357,0.0031</t>
+  </si>
+  <si>
+    <t>0.1031,0.2311,0.7557,0.0024</t>
+  </si>
+  <si>
+    <t>0.0559,0.0070,0.9678,0.0022</t>
+  </si>
+  <si>
+    <t>0.5097,0.0060,0.7273,0.0021</t>
+  </si>
+  <si>
+    <t>0.5530,0.0094,0.6474,0.0030</t>
+  </si>
+  <si>
+    <t>0.2434,0.0045,0.8821,0.0018</t>
+  </si>
+  <si>
+    <t>0.1032,0.0080,0.9449,0.0031</t>
+  </si>
+  <si>
+    <t>0.4182,0.0053,0.7880,0.0013</t>
+  </si>
+  <si>
+    <t>0.9644,0.0146,0.0274,0.0021</t>
+  </si>
+  <si>
+    <t>0.9458,0.0251,0.0381,0.0041</t>
+  </si>
+  <si>
+    <t>0.9289,0.0213,0.0676,0.0029</t>
+  </si>
+  <si>
+    <t>0.5577,0.0126,0.6119,0.0031</t>
+  </si>
+  <si>
+    <t>0.9517,0.0146,0.0444,0.0029</t>
+  </si>
+  <si>
+    <t>0.9427,0.0270,0.0382,0.0029</t>
+  </si>
+  <si>
+    <t>0.9625,0.0168,0.0244,0.0024</t>
+  </si>
+  <si>
+    <t>0.0479,0.0469,0.9514,0.0015</t>
+  </si>
+  <si>
+    <t>0.0534,0.0081,0.9722,0.0014</t>
+  </si>
+  <si>
+    <t>0.1660,0.0090,0.9147,0.0021</t>
+  </si>
+  <si>
+    <t>0.0111,0.0852,0.9804,0.0019</t>
+  </si>
+  <si>
+    <t>0.1694,0.0064,0.9134,0.0018</t>
+  </si>
+  <si>
+    <t>0.2740,0.1936,0.4906,0.0049</t>
+  </si>
+  <si>
+    <t>0.0365,0.5055,0.7880,0.0047</t>
+  </si>
+  <si>
+    <t>0.9288,0.0154,0.0843,0.0025</t>
+  </si>
+  <si>
+    <t>0.9308,0.0167,0.0835,0.0030</t>
+  </si>
+  <si>
+    <t>0.0765,0.0198,0.9361,0.0053</t>
+  </si>
+  <si>
+    <t>0.0666,0.0894,0.9131,0.0017</t>
+  </si>
+  <si>
+    <t>0.2012,0.0142,0.8889,0.0017</t>
+  </si>
+  <si>
+    <t>0.0426,0.0506,0.9511,0.0015</t>
+  </si>
+  <si>
+    <t>0.0593,0.0211,0.9575,0.0012</t>
+  </si>
+  <si>
+    <t>0.9663,0.0078,0.0355,0.0025</t>
+  </si>
+  <si>
+    <t>0.9502,0.0114,0.0475,0.0053</t>
+  </si>
+  <si>
+    <t>0.9406,0.0084,0.0867,0.0029</t>
+  </si>
+  <si>
+    <t>0.9386,0.0096,0.0799,0.0047</t>
+  </si>
+  <si>
+    <t>0.9068,0.0193,0.1067,0.0062</t>
+  </si>
+  <si>
+    <t>0.9574,0.0094,0.0452,0.0033</t>
+  </si>
+  <si>
+    <t>0.0793,0.0128,0.9556,0.0016</t>
+  </si>
+  <si>
+    <t>0.0484,0.0096,0.9731,0.0010</t>
+  </si>
+  <si>
+    <t>0.2165,0.0399,0.7984,0.0017</t>
+  </si>
+  <si>
+    <t>0.2843,0.0086,0.8519,0.0024</t>
+  </si>
+  <si>
+    <t>0.0214,0.0365,0.9779,0.0007</t>
+  </si>
+  <si>
+    <t>0.2294,0.0127,0.8550,0.0016</t>
+  </si>
+  <si>
+    <t>0.9371,0.0330,0.0384,0.0036</t>
+  </si>
+  <si>
+    <t>0.9626,0.0146,0.0271,0.0025</t>
+  </si>
+  <si>
+    <t>0.9506,0.0220,0.0341,0.0028</t>
+  </si>
+  <si>
+    <t>0.9412,0.0289,0.0376,0.0042</t>
+  </si>
+  <si>
+    <t>0.9411,0.0240,0.0438,0.0029</t>
+  </si>
+  <si>
+    <t>0.9305,0.0276,0.0552,0.0052</t>
+  </si>
+  <si>
+    <t>0.9031,0.0239,0.1180,0.0022</t>
+  </si>
+  <si>
+    <t>0.9468,0.0267,0.0323,0.0036</t>
+  </si>
+  <si>
+    <t>0.9041,0.0425,0.0726,0.0054</t>
+  </si>
+  <si>
+    <t>0.9245,0.0286,0.0608,0.0025</t>
+  </si>
+  <si>
+    <t>0.9693,0.0114,0.0257,0.0018</t>
+  </si>
+  <si>
+    <t>0.9456,0.0181,0.0534,0.0030</t>
+  </si>
+  <si>
+    <t>0.9605,0.0155,0.0261,0.0030</t>
+  </si>
+  <si>
+    <t>0.9434,0.0245,0.0402,0.0037</t>
+  </si>
+  <si>
+    <t>0.9238,0.0273,0.0640,0.0053</t>
+  </si>
+  <si>
+    <t>0.9448,0.0266,0.0368,0.0024</t>
+  </si>
+  <si>
+    <t>0.0587,0.0087,0.9629,0.0037</t>
+  </si>
+  <si>
+    <t>0.5351,0.0103,0.6524,0.0024</t>
+  </si>
+  <si>
+    <t>0.8774,0.0069,0.2499,0.0014</t>
+  </si>
+  <si>
+    <t>0.6722,0.0095,0.5496,0.0022</t>
+  </si>
+  <si>
+    <t>0.8686,0.0707,0.0668,0.0041</t>
+  </si>
+  <si>
+    <t>0.7638,0.0816,0.1511,0.0042</t>
+  </si>
+  <si>
+    <t>0.9370,0.0274,0.0385,0.0037</t>
+  </si>
+  <si>
+    <t>0.8628,0.0638,0.0841,0.0040</t>
+  </si>
+  <si>
+    <t>0.6468,0.1232,0.2311,0.0075</t>
+  </si>
+  <si>
+    <t>0.6368,0.1585,0.1582,0.0056</t>
+  </si>
+  <si>
+    <t>0.9270,0.0237,0.0666,0.0024</t>
+  </si>
+  <si>
+    <t>0.8490,0.0141,0.2320,0.0032</t>
+  </si>
+  <si>
+    <t>0.8996,0.0054,0.2034,0.0014</t>
+  </si>
+  <si>
+    <t>0.8207,0.0164,0.2676,0.0017</t>
+  </si>
+  <si>
+    <t>0.8476,0.0152,0.2372,0.0029</t>
+  </si>
+  <si>
+    <t>0.9449,0.0081,0.0767,0.0024</t>
+  </si>
+  <si>
+    <t>0.2889,0.1094,0.5952,0.0035</t>
+  </si>
+  <si>
+    <t>0.2171,0.1904,0.5301,0.0048</t>
+  </si>
+  <si>
+    <t>0.8927,0.0197,0.1352,0.0037</t>
+  </si>
+  <si>
+    <t>0.0492,0.2135,0.8780,0.0034</t>
+  </si>
+  <si>
+    <t>0.8327,0.0382,0.1835,0.0033</t>
+  </si>
+  <si>
+    <t>0.8675,0.0413,0.1238,0.0041</t>
+  </si>
+  <si>
+    <t>0.8926,0.0267,0.1163,0.0031</t>
+  </si>
+  <si>
+    <t>0.9051,0.0298,0.0921,0.0045</t>
+  </si>
+  <si>
+    <t>0.9463,0.0234,0.0367,0.0036</t>
+  </si>
+  <si>
+    <t>0.9328,0.0309,0.0468,0.0043</t>
+  </si>
+  <si>
+    <t>0.9492,0.0160,0.0523,0.0032</t>
+  </si>
+  <si>
+    <t>0.9554,0.0167,0.0366,0.0029</t>
+  </si>
+  <si>
+    <t>0.9511,0.0150,0.0414,0.0019</t>
+  </si>
+  <si>
+    <t>0.9415,0.0145,0.0588,0.0036</t>
+  </si>
+  <si>
+    <t>0.9394,0.0151,0.0683,0.0027</t>
+  </si>
+  <si>
+    <t>0.0417,0.0266,0.9621,0.0014</t>
+  </si>
+  <si>
+    <t>0.1087,0.0191,0.9281,0.0012</t>
+  </si>
+  <si>
+    <t>0.2591,0.0046,0.8836,0.0012</t>
+  </si>
+  <si>
+    <t>0.2235,0.0117,0.8720,0.0013</t>
+  </si>
+  <si>
+    <t>0.9290,0.0147,0.0858,0.0031</t>
+  </si>
+  <si>
+    <t>0.8737,0.0171,0.1834,0.0036</t>
+  </si>
+  <si>
+    <t>0.8797,0.0082,0.2151,0.0017</t>
+  </si>
+  <si>
+    <t>0.9090,0.0157,0.1184,0.0023</t>
+  </si>
+  <si>
+    <t>0.9626,0.0085,0.0432,0.0033</t>
+  </si>
+  <si>
+    <t>0.8779,0.0169,0.1613,0.0095</t>
+  </si>
+  <si>
+    <t>0.9225,0.0101,0.1263,0.0052</t>
+  </si>
+  <si>
+    <t>0.9453,0.0085,0.0658,0.0048</t>
+  </si>
+  <si>
+    <t>0.1337,0.1223,0.8293,0.0056</t>
+  </si>
+  <si>
+    <t>0.9514,0.0155,0.0469,0.0030</t>
+  </si>
+  <si>
+    <t>0.9182,0.0229,0.0736,0.0037</t>
+  </si>
+  <si>
+    <t>0.9604,0.0148,0.0310,0.0030</t>
+  </si>
+  <si>
+    <t>0.9227,0.0314,0.0654,0.0038</t>
+  </si>
+  <si>
+    <t>0.9412,0.0186,0.0568,0.0040</t>
+  </si>
+  <si>
+    <t>0.9079,0.0154,0.1371,0.0039</t>
+  </si>
+  <si>
+    <t>0.9607,0.0121,0.0414,0.0024</t>
+  </si>
+  <si>
+    <t>0.0349,0.0167,0.9680,0.0085</t>
+  </si>
+  <si>
+    <t>0.9569,0.0076,0.0638,0.0021</t>
+  </si>
+  <si>
+    <t>0.9562,0.0131,0.0474,0.0026</t>
+  </si>
+  <si>
+    <t>0.8828,0.0147,0.1854,0.0053</t>
+  </si>
+  <si>
+    <t>0.9197,0.0168,0.0983,0.0038</t>
+  </si>
+  <si>
+    <t>0.9322,0.0133,0.0857,0.0024</t>
+  </si>
+  <si>
+    <t>0.8718,0.0313,0.1414,0.0047</t>
+  </si>
+  <si>
+    <t>0.9413,0.0137,0.0646,0.0027</t>
+  </si>
+  <si>
+    <t>0.9152,0.0248,0.0844,0.0034</t>
+  </si>
+  <si>
+    <t>0.9476,0.0152,0.0599,0.0020</t>
+  </si>
+  <si>
+    <t>0.9689,0.0112,0.0267,0.0022</t>
+  </si>
+  <si>
+    <t>0.9583,0.0115,0.0464,0.0028</t>
+  </si>
+  <si>
+    <t>0.9495,0.0153,0.0505,0.0032</t>
+  </si>
+  <si>
+    <t>0.9344,0.0236,0.0558,0.0031</t>
+  </si>
+  <si>
+    <t>0.9264,0.0247,0.0659,0.0062</t>
+  </si>
+  <si>
+    <t>0.9362,0.0240,0.0491,0.0036</t>
+  </si>
+  <si>
+    <t>0.9655,0.0146,0.0225,0.0020</t>
+  </si>
+  <si>
+    <t>0.8408,0.0823,0.0700,0.0038</t>
+  </si>
+  <si>
+    <t>0.8611,0.0653,0.0834,0.0042</t>
+  </si>
+  <si>
+    <t>0.9107,0.0408,0.0524,0.0041</t>
+  </si>
+  <si>
+    <t>0.8790,0.0250,0.1371,0.0046</t>
+  </si>
+  <si>
+    <t>0.9282,0.0250,0.0558,0.0031</t>
+  </si>
+  <si>
+    <t>0.9410,0.0201,0.0519,0.0043</t>
+  </si>
+  <si>
+    <t>0.9290,0.0231,0.0644,0.0026</t>
+  </si>
+  <si>
+    <t>0.9517,0.0177,0.0385,0.0024</t>
+  </si>
+  <si>
+    <t>0.1404,0.0084,0.9356,0.0025</t>
+  </si>
+  <si>
+    <t>0.9482,0.0107,0.0740,0.0018</t>
+  </si>
+  <si>
+    <t>0.3588,0.0046,0.8276,0.0014</t>
+  </si>
+  <si>
+    <t>0.1579,0.0056,0.9207,0.0017</t>
+  </si>
+  <si>
+    <t>0.8036,0.0079,0.3601,0.0017</t>
+  </si>
+  <si>
+    <t>0.1387,0.0066,0.9255,0.0013</t>
+  </si>
+  <si>
+    <t>0.3427,0.0078,0.8292,0.0014</t>
+  </si>
+  <si>
+    <t>0.4214,0.0053,0.7883,0.0012</t>
+  </si>
+  <si>
+    <t>0.4407,0.0087,0.7457,0.0022</t>
+  </si>
+  <si>
+    <t>0.7718,0.0095,0.4005,0.0024</t>
+  </si>
+  <si>
+    <t>0.8553,0.0169,0.2024,0.0029</t>
+  </si>
+  <si>
+    <t>0.8365,0.0201,0.2329,0.0032</t>
+  </si>
+  <si>
+    <t>0.8667,0.0123,0.2203,0.0020</t>
+  </si>
+  <si>
+    <t>0.8797,0.0107,0.2194,0.0022</t>
+  </si>
+  <si>
+    <t>0.9177,0.0093,0.1465,0.0014</t>
+  </si>
+  <si>
+    <t>0.7642,0.0208,0.3292,0.0032</t>
+  </si>
+  <si>
+    <t>0.8547,0.0108,0.2341,0.0018</t>
+  </si>
+  <si>
+    <t>0.9142,0.0424,0.0494,0.0052</t>
+  </si>
+  <si>
+    <t>0.9504,0.0245,0.0306,0.0025</t>
+  </si>
+  <si>
+    <t>0.9093,0.0333,0.0743,0.0046</t>
+  </si>
+  <si>
+    <t>0.9620,0.0136,0.0326,0.0020</t>
+  </si>
+  <si>
+    <t>0.9363,0.0318,0.0427,0.0036</t>
+  </si>
+  <si>
+    <t>0.7964,0.0201,0.2735,0.0036</t>
+  </si>
+  <si>
+    <t>0.8554,0.0134,0.2513,0.0022</t>
+  </si>
+  <si>
+    <t>0.9094,0.0070,0.1698,0.0028</t>
+  </si>
+  <si>
+    <t>0.8586,0.0065,0.2819,0.0018</t>
+  </si>
+  <si>
+    <t>0.8254,0.0100,0.3183,0.0035</t>
+  </si>
+  <si>
+    <t>0.5292,0.0062,0.6888,0.0021</t>
+  </si>
+  <si>
+    <t>0.0704,0.0330,0.9439,0.0014</t>
+  </si>
+  <si>
+    <t>0.4987,0.0074,0.7322,0.0011</t>
+  </si>
+  <si>
+    <t>0.5390,0.0047,0.7077,0.0010</t>
+  </si>
+  <si>
+    <t>0.4062,0.0162,0.7438,0.0023</t>
+  </si>
+  <si>
+    <t>0.9540,0.0180,0.0297,0.0042</t>
+  </si>
+  <si>
+    <t>0.9444,0.0155,0.0624,0.0026</t>
+  </si>
+  <si>
+    <t>0.9484,0.0190,0.0371,0.0033</t>
+  </si>
+  <si>
+    <t>0.9343,0.0249,0.0520,0.0060</t>
+  </si>
+  <si>
+    <t>0.9112,0.0339,0.0731,0.0039</t>
+  </si>
+  <si>
+    <t>0.9534,0.0189,0.0372,0.0035</t>
+  </si>
+  <si>
+    <t>0.9314,0.0280,0.0556,0.0036</t>
+  </si>
+  <si>
+    <t>0.9494,0.0203,0.0406,0.0025</t>
+  </si>
+  <si>
+    <t>0.6989,0.0104,0.5311,0.0026</t>
+  </si>
+  <si>
+    <t>0.9228,0.0142,0.1032,0.0036</t>
+  </si>
+  <si>
+    <t>0.9384,0.0130,0.0798,0.0029</t>
+  </si>
+  <si>
+    <t>0.6446,0.0046,0.6045,0.0024</t>
+  </si>
+  <si>
+    <t>0.0611,0.0066,0.9686,0.0030</t>
+  </si>
+  <si>
+    <t>0.4229,0.0077,0.7473,0.0019</t>
+  </si>
+  <si>
+    <t>0.0913,0.0053,0.9547,0.0028</t>
+  </si>
+  <si>
+    <t>0.7146,0.0060,0.5184,0.0013</t>
+  </si>
+  <si>
+    <t>0.0654,0.0121,0.9613,0.0052</t>
+  </si>
+  <si>
+    <t>0.1477,0.0073,0.9205,0.0016</t>
+  </si>
+  <si>
+    <t>0.7559,0.0089,0.4340,0.0022</t>
+  </si>
+  <si>
+    <t>0.7935,0.0076,0.3994,0.0026</t>
+  </si>
+  <si>
+    <t>0.9177,0.0074,0.1441,0.0021</t>
+  </si>
+  <si>
+    <t>0.8655,0.0067,0.2923,0.0020</t>
+  </si>
+  <si>
+    <t>0.9433,0.0316,0.0294,0.0035</t>
+  </si>
+  <si>
+    <t>0.9217,0.0336,0.0640,0.0043</t>
+  </si>
+  <si>
+    <t>0.9265,0.0302,0.0572,0.0038</t>
+  </si>
+  <si>
+    <t>0.9469,0.0242,0.0324,0.0037</t>
+  </si>
+  <si>
+    <t>0.9654,0.0159,0.0257,0.0026</t>
+  </si>
+  <si>
+    <t>0.9340,0.0271,0.0476,0.0028</t>
+  </si>
+  <si>
+    <t>0.9540,0.0216,0.0316,0.0023</t>
+  </si>
+  <si>
+    <t>0.9322,0.0198,0.0686,0.0033</t>
+  </si>
+  <si>
+    <t>0.3208,0.0107,0.8139,0.0016</t>
+  </si>
+  <si>
+    <t>0.0941,0.0111,0.9460,0.0017</t>
+  </si>
+  <si>
+    <t>0.1866,0.0058,0.9042,0.0019</t>
+  </si>
+  <si>
+    <t>0.6183,0.0086,0.5930,0.0017</t>
+  </si>
+  <si>
+    <t>0.6236,0.0062,0.6166,0.0018</t>
+  </si>
+  <si>
+    <t>0.7340,0.0096,0.4728,0.0038</t>
+  </si>
+  <si>
+    <t>0.4748,0.0081,0.7398,0.0018</t>
+  </si>
+  <si>
+    <t>0.3166,0.0097,0.8406,0.0036</t>
+  </si>
+  <si>
+    <t>0.9537,0.0092,0.0606,0.0020</t>
+  </si>
+  <si>
+    <t>0.9267,0.0078,0.1325,0.0032</t>
+  </si>
+  <si>
+    <t>0.9420,0.0129,0.0557,0.0051</t>
+  </si>
+  <si>
+    <t>0.9474,0.0110,0.0435,0.0075</t>
+  </si>
+  <si>
+    <t>0.9598,0.0069,0.0552,0.0040</t>
+  </si>
+  <si>
+    <t>0.9355,0.0107,0.0891,0.0028</t>
   </si>
 </sst>
 </file>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2261,7 +2261,7 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
         <v>286</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2891,7 +2891,7 @@
         <v>262</v>
       </c>
       <c r="C69" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D69" t="s">
         <v>331</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4669,7 +4669,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
         <v>458</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
